--- a/sample-data/매출요약.xlsx
+++ b/sample-data/매출요약.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="월별매출" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="메모" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별매출" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메모" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/sample-data/매출요약.xlsx
+++ b/sample-data/매출요약.xlsx
@@ -1,68 +1,169 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별매출" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메모" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet sheetId="1" name="월별매출" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="메모" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+  <si>
+    <t>2026년 상반기 매출 요약</t>
+  </si>
+  <si>
+    <t>월</t>
+  </si>
+  <si>
+    <t>제품A</t>
+  </si>
+  <si>
+    <t>제품B</t>
+  </si>
+  <si>
+    <t>제품C</t>
+  </si>
+  <si>
+    <t>합계</t>
+  </si>
+  <si>
+    <t>1월</t>
+  </si>
+  <si>
+    <t>1200000</t>
+  </si>
+  <si>
+    <t>980000</t>
+  </si>
+  <si>
+    <t>450000</t>
+  </si>
+  <si>
+    <t>2월</t>
+  </si>
+  <si>
+    <t>1350000</t>
+  </si>
+  <si>
+    <t>1010000</t>
+  </si>
+  <si>
+    <t>520000</t>
+  </si>
+  <si>
+    <t>3월</t>
+  </si>
+  <si>
+    <t>1500000</t>
+  </si>
+  <si>
+    <t>1100000</t>
+  </si>
+  <si>
+    <t>610000</t>
+  </si>
+  <si>
+    <t>4월</t>
+  </si>
+  <si>
+    <t>1420000</t>
+  </si>
+  <si>
+    <t>1250000</t>
+  </si>
+  <si>
+    <t>700000</t>
+  </si>
+  <si>
+    <t>5월</t>
+  </si>
+  <si>
+    <t>1680000</t>
+  </si>
+  <si>
+    <t>1330000</t>
+  </si>
+  <si>
+    <t>760000</t>
+  </si>
+  <si>
+    <t>6월</t>
+  </si>
+  <si>
+    <t>1810000</t>
+  </si>
+  <si>
+    <t>1400000</t>
+  </si>
+  <si>
+    <t>820000</t>
+  </si>
+  <si>
+    <t>저장 라운드트립 OK</t>
+  </si>
+  <si>
+    <t>이 시트는 두 번째 시트입니다.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
       <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="14"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
-      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00C00000"/>
+      <b/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FFC00000"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E639C"/>
+        <fgColor rgb="FF0E639C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -70,109 +171,36 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BBBBBB"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BBBBBB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BBBBBB"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -251,6 +279,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -285,6 +314,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -319,20 +349,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -454,206 +480,219 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="11.142857142857142" customWidth="1"/>
+    <col min="2" max="5" width="15.714285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>2026년 상반기 매출 요약</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>월</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>제품A</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>제품B</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>제품C</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>1월</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>980000</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>450000</v>
+    <row r="1" ht="27.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="E3" s="5">
         <f>SUM(B3:D3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>2월</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>1010000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>520000</v>
+        <v>2630000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="E4" s="5">
         <f>SUM(B4:D4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>3월</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>610000</v>
+        <v>2880000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="E5" s="5">
         <f>SUM(B5:D5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>4월</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>1420000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1250000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>700000</v>
+        <v>3210000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="E6" s="5">
         <f>SUM(B6:D6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>5월</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>1680000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>1330000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>760000</v>
+        <v>3370000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="E7" s="5">
         <f>SUM(B7:D7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>6월</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>1810000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>820000</v>
+        <v>3770000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="E8" s="5">
         <f>SUM(B8:D8)</f>
-        <v/>
+        <v>4030000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>이 시트는 두 번째 시트입니다.</t>
-        </is>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/sample-data/매출요약.xlsx
+++ b/sample-data/매출요약.xlsx
@@ -1,169 +1,68 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="월별매출" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="메모" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별매출" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메모" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
-  <si>
-    <t>2026년 상반기 매출 요약</t>
-  </si>
-  <si>
-    <t>월</t>
-  </si>
-  <si>
-    <t>제품A</t>
-  </si>
-  <si>
-    <t>제품B</t>
-  </si>
-  <si>
-    <t>제품C</t>
-  </si>
-  <si>
-    <t>합계</t>
-  </si>
-  <si>
-    <t>1월</t>
-  </si>
-  <si>
-    <t>1200000</t>
-  </si>
-  <si>
-    <t>980000</t>
-  </si>
-  <si>
-    <t>450000</t>
-  </si>
-  <si>
-    <t>2월</t>
-  </si>
-  <si>
-    <t>1350000</t>
-  </si>
-  <si>
-    <t>1010000</t>
-  </si>
-  <si>
-    <t>520000</t>
-  </si>
-  <si>
-    <t>3월</t>
-  </si>
-  <si>
-    <t>1500000</t>
-  </si>
-  <si>
-    <t>1100000</t>
-  </si>
-  <si>
-    <t>610000</t>
-  </si>
-  <si>
-    <t>4월</t>
-  </si>
-  <si>
-    <t>1420000</t>
-  </si>
-  <si>
-    <t>1250000</t>
-  </si>
-  <si>
-    <t>700000</t>
-  </si>
-  <si>
-    <t>5월</t>
-  </si>
-  <si>
-    <t>1680000</t>
-  </si>
-  <si>
-    <t>1330000</t>
-  </si>
-  <si>
-    <t>760000</t>
-  </si>
-  <si>
-    <t>6월</t>
-  </si>
-  <si>
-    <t>1810000</t>
-  </si>
-  <si>
-    <t>1400000</t>
-  </si>
-  <si>
-    <t>820000</t>
-  </si>
-  <si>
-    <t>저장 라운드트립 OK</t>
-  </si>
-  <si>
-    <t>이 시트는 두 번째 시트입니다.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
     <font>
-      <b/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FFC00000"/>
+      <i val="1"/>
+      <color rgb="00C00000"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E639C"/>
+        <fgColor rgb="000E639C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
+        <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -171,36 +70,109 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -279,7 +251,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -314,7 +285,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -349,16 +319,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -480,219 +454,206 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.142857142857142" customWidth="1"/>
-    <col min="2" max="5" width="15.714285714285714" customWidth="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>2026년 상반기 매출 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>제품A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>제품B</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>제품C</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>1월</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>980000</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>450000</v>
       </c>
       <c r="E3" s="5">
         <f>SUM(B3:D3)</f>
-        <v>2630000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>13</v>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2월</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1010000</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>520000</v>
       </c>
       <c r="E4" s="5">
         <f>SUM(B4:D4)</f>
-        <v>2880000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>17</v>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>3월</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>610000</v>
       </c>
       <c r="E5" s="5">
         <f>SUM(B5:D5)</f>
-        <v>3210000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>21</v>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>4월</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>1420000</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>700000</v>
       </c>
       <c r="E6" s="5">
         <f>SUM(B6:D6)</f>
-        <v>3370000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>25</v>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>5월</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>1680000</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>1330000</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>760000</v>
       </c>
       <c r="E7" s="5">
         <f>SUM(B7:D7)</f>
-        <v>3770000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>29</v>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>6월</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>1810000</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>820000</v>
       </c>
       <c r="E8" s="5">
         <f>SUM(B8:D8)</f>
-        <v>4030000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>30</v>
+        <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>31</v>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>이 시트는 두 번째 시트입니다.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>